--- a/EndResult/50m Butterfly.xlsx
+++ b/EndResult/50m Butterfly.xlsx
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,46</t>
+          <t>26,23</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.07.2025</t>
+          <t>18.04.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rud</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28,37</t>
+          <t>27,90</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>634</v>
+        <v>667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sara Alonso Lopez</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29,97</t>
+          <t>29,96</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31.10.2021</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Sara Alonso Lopez</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,96</t>
+          <t>29,97</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>31.10.2021</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1679,20 +1679,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28,60</t>
+          <t>28,01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04.04.2025</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1814,25 +1814,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alma van der Hagen</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,50</t>
+          <t>29,43</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.04.2025</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1849,25 +1849,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karoline Borg Simonsen</t>
+          <t>Alma van der Hagen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,81</t>
+          <t>29,50</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>04.04.2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1884,25 +1884,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vilde Holan Bye</t>
+          <t>Karoline Borg Simonsen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29,91</t>
+          <t>29,81</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>06.07.2013</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1919,25 +1919,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Henriette Martinsen</t>
+          <t>Vilde Holan Bye</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,24</t>
+          <t>29,91</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.07.2008</t>
+          <t>06.07.2013</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1954,25 +1954,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Henriette Martinsen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,37</t>
+          <t>30,24</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07.07.2013</t>
+          <t>13.07.2008</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1989,20 +1989,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sara Alonso Lopez</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30,43</t>
+          <t>30,37</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.01.2023</t>
+          <t>07.07.2013</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
